--- a/Scripts/IMTB_Scenarios_template.xlsx
+++ b/Scripts/IMTB_Scenarios_template.xlsx
@@ -486,8 +486,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A083C8BB3CC8064ABDA6C45A5EE4EDBD" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cca73d0fe585e66a18d7843fdac0e42a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="5555c9e0-38a5-43bc-89d0-52a71534209e" xmlns:ns3="cd7aea5e-f8be-4077-915f-c791ea3e0497" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d5da8d89b1f3f736f86bb71d2fdd5335" ns1:_="" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A083C8BB3CC8064ABDA6C45A5EE4EDBD" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="72473ef79cc7e9a4b403aa49ee94d9fa">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="5555c9e0-38a5-43bc-89d0-52a71534209e" xmlns:ns3="cd7aea5e-f8be-4077-915f-c791ea3e0497" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="86c384d25b58a3ee3ec928dfd18c0f47" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="5555c9e0-38a5-43bc-89d0-52a71534209e"/>
     <xsd:import namespace="cd7aea5e-f8be-4077-915f-c791ea3e0497"/>
@@ -779,7 +779,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{46ED7D40-7229-43B0-A908-87171088602C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{650EB635-CD7C-47F9-B681-54B916038C9E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
